--- a/data/templates/template_month_advance_given.xlsx
+++ b/data/templates/template_month_advance_given.xlsx
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ביטוח רפואי ל{{worker_role}} - שולם באמצעות סוכנות ביטוח הילית בחברת הראל  - קופ"ח  כללית </t>
+          <t xml:space="preserve">ביטוח רפואי ל{{worker_role}} - שולם באמצעות {{insurer}}</t>
         </is>
       </c>
       <c r="C10" s="110" t="n"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B21" s="152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ביטוח לאומי. - הפרשות בגין חודשים               - התשלום  בוצע  ב  </t>
+          <t xml:space="preserve">ביטוח לאומי. - הפרשות בגין חודשים {{ni_months}} - התשלום  בוצע  ב {{ni_paid_on}}</t>
         </is>
       </c>
       <c r="C21" s="137" t="n"/>
